--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130700791</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130699120</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130699002</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130700791</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130699120</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130699002</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130700791</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130699120</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130699002</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fabian  Pettersson</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fabian  Pettersson</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fabian  Pettersson</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fabian  Pettersson</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -984,15 +984,546 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fabian  Pettersson</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fabian  Pettersson</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130894504</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91796</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kilen, Kilen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>397912</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7048392</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130904210</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vallen, Vallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>397838</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7048574</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130905540</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vallen, Vallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>397970</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7048600</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130894789</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79692</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1797</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mjölig dropplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cliostomum leprosum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kilen, Kilen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>397898</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7048394</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130901126</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58500</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kilen, Kilen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>397812</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7048494</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,7 +999,7 @@
         <v>130894504</v>
       </c>
       <c r="B5" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1525,6 +1525,327 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130946525</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79222</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vallen, Vallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>397573</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7048851</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130946059</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79222</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vallen, Vallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>397590</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7048947</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130951957</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vallen, Vallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>397653</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7048765</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130700791</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130699120</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130699002</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130894504</v>
       </c>
       <c r="B5" t="n">
-        <v>91804</v>
+        <v>91818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130904210</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>79235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>130905540</v>
       </c>
       <c r="B7" t="n">
-        <v>80326</v>
+        <v>80340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>130894789</v>
       </c>
       <c r="B8" t="n">
-        <v>79692</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>130901126</v>
       </c>
       <c r="B9" t="n">
-        <v>58500</v>
+        <v>58514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130946525</v>
       </c>
       <c r="B10" t="n">
-        <v>79222</v>
+        <v>79236</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>130946059</v>
       </c>
       <c r="B11" t="n">
-        <v>79222</v>
+        <v>79236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>130951957</v>
       </c>
       <c r="B12" t="n">
-        <v>80326</v>
+        <v>80340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130904210</v>
+        <v>130905540</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397838</v>
+        <v>397970</v>
       </c>
       <c r="R6" t="n">
-        <v>7048574</v>
+        <v>7048600</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130905540</v>
+        <v>130904210</v>
       </c>
       <c r="B7" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397970</v>
+        <v>397838</v>
       </c>
       <c r="R7" t="n">
-        <v>7048600</v>
+        <v>7048574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130905540</v>
+        <v>130904210</v>
       </c>
       <c r="B6" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397970</v>
+        <v>397838</v>
       </c>
       <c r="R6" t="n">
-        <v>7048600</v>
+        <v>7048574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130904210</v>
+        <v>130905540</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397838</v>
+        <v>397970</v>
       </c>
       <c r="R7" t="n">
-        <v>7048574</v>
+        <v>7048600</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130894504</v>
       </c>
       <c r="B5" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130904210</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>130905540</v>
       </c>
       <c r="B7" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>130894789</v>
       </c>
       <c r="B8" t="n">
-        <v>79715</v>
+        <v>79716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>130901126</v>
       </c>
       <c r="B9" t="n">
-        <v>58520</v>
+        <v>58521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130946525</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>130946059</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>130951957</v>
       </c>
       <c r="B12" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>131063376</v>
       </c>
       <c r="B13" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131061121</v>
       </c>
       <c r="B14" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131060978</v>
       </c>
       <c r="B15" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -1851,7 +1851,7 @@
         <v>131063376</v>
       </c>
       <c r="B13" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131061121</v>
       </c>
       <c r="B14" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131060978</v>
       </c>
       <c r="B15" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -1851,7 +1851,7 @@
         <v>131063376</v>
       </c>
       <c r="B13" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131061121</v>
       </c>
       <c r="B14" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131060978</v>
       </c>
       <c r="B15" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -1851,7 +1851,7 @@
         <v>131063376</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131061121</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131060978</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -1851,7 +1851,7 @@
         <v>131063376</v>
       </c>
       <c r="B13" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131061121</v>
       </c>
       <c r="B14" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131060978</v>
       </c>
       <c r="B15" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -1851,7 +1851,7 @@
         <v>131063376</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>131061121</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>131060978</v>
       </c>
       <c r="B15" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130700791</v>
+        <v>130894789</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1797</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallen, Vallen, Jmt</t>
+          <t>Kilen, Kilen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397955</v>
+        <v>397898</v>
       </c>
       <c r="R2" t="n">
-        <v>7048702</v>
+        <v>7048394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130699120</v>
+        <v>130699002</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -820,7 +820,7 @@
         <v>398087</v>
       </c>
       <c r="R3" t="n">
-        <v>7048738</v>
+        <v>7048749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130699002</v>
+        <v>130699120</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -927,7 +927,7 @@
         <v>398087</v>
       </c>
       <c r="R4" t="n">
-        <v>7048749</v>
+        <v>7048738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,41 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130894504</v>
+        <v>130700791</v>
       </c>
       <c r="B5" t="n">
-        <v>91830</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilen, Kilen, Jmt</t>
+          <t>Vallen, Vallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397912</v>
+        <v>397955</v>
       </c>
       <c r="R5" t="n">
-        <v>7048392</v>
+        <v>7048702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,11 +1106,11 @@
         <v>130904210</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1209,7 +1213,7 @@
         <v>130905540</v>
       </c>
       <c r="B7" t="n">
-        <v>80350</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130894789</v>
+        <v>130951957</v>
       </c>
       <c r="B8" t="n">
-        <v>79716</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,34 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1797</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kilen, Kilen, Jmt</t>
+          <t>Vallen, Vallen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397898</v>
+        <v>397653</v>
       </c>
       <c r="R8" t="n">
-        <v>7048394</v>
+        <v>7048765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,45 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130901126</v>
+        <v>130952759</v>
       </c>
       <c r="B9" t="n">
-        <v>58521</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kilen, Kilen, Jmt</t>
+          <t>Vallen, Vallen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>397812</v>
+        <v>397636</v>
       </c>
       <c r="R9" t="n">
-        <v>7048494</v>
+        <v>7048659</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,45 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130946525</v>
+        <v>130952687</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vallen, Vallen, Jmt</t>
+          <t>Vallen, Kilen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>397573</v>
+        <v>397638</v>
       </c>
       <c r="R10" t="n">
-        <v>7048851</v>
+        <v>7048667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,45 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130946059</v>
+        <v>130901126</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>58592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>102125</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallen, Vallen, Jmt</t>
+          <t>Kilen, Kilen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>397590</v>
+        <v>397812</v>
       </c>
       <c r="R11" t="n">
-        <v>7048947</v>
+        <v>7048494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,22 +1703,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130951957</v>
+        <v>130946059</v>
       </c>
       <c r="B12" t="n">
-        <v>80350</v>
+        <v>79328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>397653</v>
+        <v>397590</v>
       </c>
       <c r="R12" t="n">
-        <v>7048765</v>
+        <v>7048947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,30 +1852,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131063376</v>
+        <v>130946417</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1879,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>397688</v>
+        <v>397532</v>
       </c>
       <c r="R13" t="n">
-        <v>7048558</v>
+        <v>7048867</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,22 +1917,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,6 +1943,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1951,30 +1964,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131061121</v>
+        <v>130946525</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>79328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1982,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397980</v>
+        <v>397573</v>
       </c>
       <c r="R14" t="n">
-        <v>7048389</v>
+        <v>7048851</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,22 +2029,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,41 +2071,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131060978</v>
+        <v>130952656</v>
       </c>
       <c r="B15" t="n">
-        <v>91838</v>
+        <v>79328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vallen, Vallen, Jmt</t>
+          <t>Vallen, Kilen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397981</v>
+        <v>397639</v>
       </c>
       <c r="R15" t="n">
-        <v>7048398</v>
+        <v>7048653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,22 +2136,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 63363-2025 artfynd.xlsx
+++ b/artfynd/A 63363-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130894789</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130700791</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130904210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130905540</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130951957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130952759</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130952687</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130901126</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130946059</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130946417</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130946525</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130952656</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130699002</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,8 +2245,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130699120</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>